--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Data/chara_talk.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Data/chara_talk.xlsx
@@ -11,7 +11,7 @@
     <sheet name="1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$136</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$137</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="305">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -101,6 +101,44 @@
 삐갸아아앗!
 삐갸아아ー아아!
 삐…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fusion2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">엔탱글!
+하나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">둘!
+꼬오옥!
+집합～!</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">play_baby</t>
@@ -2329,7 +2367,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2353,6 +2391,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
       <charset val="129"/>
     </font>
     <font>
@@ -2433,7 +2478,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2441,7 +2486,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2489,9 +2534,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>2374200</xdr:colOff>
+      <xdr:colOff>2373840</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>122400</xdr:rowOff>
+      <xdr:rowOff>122040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2501,7 +2546,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="50978880" cy="122400"/>
+          <a:ext cx="50978520" cy="122040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2534,9 +2579,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>513720</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>60840</xdr:rowOff>
+      <xdr:colOff>513360</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>60480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2546,7 +2591,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="55506600" cy="46861560"/>
+          <a:ext cx="55506240" cy="47410560"/>
         </a:xfrm>
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
@@ -2681,7 +2726,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CM137"/>
+  <dimension ref="A1:CM138"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.04"/>
@@ -2930,13 +2975,14 @@
       <c r="AU5" s="3"/>
       <c r="AV5" s="3"/>
     </row>
-    <row r="6" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="C6" s="4"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
@@ -2966,7 +3012,7 @@
       <c r="AU6" s="3"/>
       <c r="AV6" s="3"/>
     </row>
-    <row r="7" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
@@ -3002,11 +3048,11 @@
       <c r="AU7" s="3"/>
       <c r="AV7" s="3"/>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>29</v>
       </c>
       <c r="U8" s="3"/>
@@ -3038,11 +3084,11 @@
       <c r="AU8" s="3"/>
       <c r="AV8" s="3"/>
     </row>
-    <row r="9" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>31</v>
       </c>
       <c r="U9" s="3"/>
@@ -3074,7 +3120,7 @@
       <c r="AU9" s="3"/>
       <c r="AV9" s="3"/>
     </row>
-    <row r="10" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>32</v>
       </c>
@@ -3110,11 +3156,11 @@
       <c r="AU10" s="3"/>
       <c r="AV10" s="3"/>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="4" t="s">
         <v>35</v>
       </c>
       <c r="U11" s="3"/>
@@ -3186,7 +3232,7 @@
       <c r="A13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="1" t="s">
         <v>39</v>
       </c>
       <c r="U13" s="3"/>
@@ -3218,11 +3264,11 @@
       <c r="AU13" s="3"/>
       <c r="AV13" s="3"/>
     </row>
-    <row r="14" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="6" t="s">
         <v>41</v>
       </c>
       <c r="U14" s="3"/>
@@ -3254,7 +3300,7 @@
       <c r="AU14" s="3"/>
       <c r="AV14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>42</v>
       </c>
@@ -3290,34 +3336,43 @@
       <c r="AU15" s="3"/>
       <c r="AV15" s="3"/>
     </row>
-    <row r="16" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="AW16" s="1"/>
-    </row>
-    <row r="17" s="3" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
+      <c r="AR16" s="3"/>
+      <c r="AS16" s="3"/>
+      <c r="AT16" s="3"/>
+      <c r="AU16" s="3"/>
+      <c r="AV16" s="3"/>
+    </row>
+    <row r="17" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>46</v>
       </c>
@@ -3371,7 +3426,7 @@
       <c r="T18" s="1"/>
       <c r="AW18" s="1"/>
     </row>
-    <row r="19" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" s="3" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>50</v>
       </c>
@@ -3398,7 +3453,7 @@
       <c r="T19" s="1"/>
       <c r="AW19" s="1"/>
     </row>
-    <row r="20" s="3" customFormat="true" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>52</v>
       </c>
@@ -3425,7 +3480,7 @@
       <c r="T20" s="1"/>
       <c r="AW20" s="1"/>
     </row>
-    <row r="21" s="3" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" s="3" customFormat="true" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>54</v>
       </c>
@@ -3452,50 +3507,40 @@
       <c r="T21" s="1"/>
       <c r="AW21" s="1"/>
     </row>
-    <row r="22" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" s="3" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
-      <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="3"/>
-      <c r="AA22" s="3"/>
-      <c r="AB22" s="3"/>
-      <c r="AC22" s="3"/>
-      <c r="AD22" s="3"/>
-      <c r="AE22" s="3"/>
-      <c r="AF22" s="3"/>
-      <c r="AG22" s="3"/>
-      <c r="AH22" s="3"/>
-      <c r="AI22" s="3"/>
-      <c r="AJ22" s="3"/>
-      <c r="AK22" s="3"/>
-      <c r="AL22" s="3"/>
-      <c r="AM22" s="3"/>
-      <c r="AN22" s="3"/>
-      <c r="AO22" s="3"/>
-      <c r="AP22" s="3"/>
-      <c r="AQ22" s="3"/>
-      <c r="AR22" s="3"/>
-      <c r="AS22" s="3"/>
-      <c r="AT22" s="3"/>
-      <c r="AU22" s="3"/>
-      <c r="AV22" s="3"/>
-    </row>
-    <row r="23" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="AW22" s="1"/>
+    </row>
+    <row r="23" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="4"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
@@ -3525,8 +3570,8 @@
       <c r="AU23" s="3"/>
       <c r="AV23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+    <row r="24" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -3562,7 +3607,7 @@
       <c r="AU24" s="3"/>
       <c r="AV24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
         <v>62</v>
       </c>
@@ -3599,7 +3644,7 @@
       <c r="AU25" s="3"/>
       <c r="AV25" s="3"/>
     </row>
-    <row r="26" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
         <v>64</v>
       </c>
@@ -3637,7 +3682,7 @@
       <c r="AV26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="4" t="s">
         <v>66</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -3673,13 +3718,14 @@
       <c r="AU27" s="3"/>
       <c r="AV27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>69</v>
       </c>
+      <c r="C28" s="4"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
@@ -3709,11 +3755,11 @@
       <c r="AU28" s="3"/>
       <c r="AV28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="4" t="s">
         <v>71</v>
       </c>
       <c r="U29" s="3"/>
@@ -3745,14 +3791,13 @@
       <c r="AU29" s="3"/>
       <c r="AV29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="146.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C30" s="7"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
@@ -3782,13 +3827,14 @@
       <c r="AU30" s="3"/>
       <c r="AV30" s="3"/>
     </row>
-    <row r="31" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="146.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="7" t="s">
         <v>75</v>
       </c>
+      <c r="C31" s="7"/>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
@@ -3818,14 +3864,13 @@
       <c r="AU31" s="3"/>
       <c r="AV31" s="3"/>
     </row>
-    <row r="32" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C32" s="4"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
@@ -3855,13 +3900,14 @@
       <c r="AU32" s="3"/>
       <c r="AV32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>79</v>
       </c>
+      <c r="C33" s="4"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
@@ -3891,7 +3937,7 @@
       <c r="AU33" s="3"/>
       <c r="AV33" s="3"/>
     </row>
-    <row r="34" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>80</v>
       </c>
@@ -3927,7 +3973,7 @@
       <c r="AU34" s="3"/>
       <c r="AV34" s="3"/>
     </row>
-    <row r="35" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>82</v>
       </c>
@@ -3963,7 +4009,7 @@
       <c r="AU35" s="3"/>
       <c r="AV35" s="3"/>
     </row>
-    <row r="36" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>84</v>
       </c>
@@ -3999,14 +4045,13 @@
       <c r="AU36" s="3"/>
       <c r="AV36" s="3"/>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C37" s="4"/>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
@@ -4036,13 +4081,14 @@
       <c r="AU37" s="3"/>
       <c r="AV37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="1" t="s">
         <v>89</v>
       </c>
+      <c r="C38" s="4"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
@@ -4072,7 +4118,7 @@
       <c r="AU38" s="3"/>
       <c r="AV38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>90</v>
       </c>
@@ -4108,7 +4154,7 @@
       <c r="AU39" s="3"/>
       <c r="AV39" s="3"/>
     </row>
-    <row r="40" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>92</v>
       </c>
@@ -4144,7 +4190,7 @@
       <c r="AU40" s="3"/>
       <c r="AV40" s="3"/>
     </row>
-    <row r="41" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>94</v>
       </c>
@@ -4180,7 +4226,7 @@
       <c r="AU41" s="3"/>
       <c r="AV41" s="3"/>
     </row>
-    <row r="42" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>96</v>
       </c>
@@ -4216,11 +4262,11 @@
       <c r="AU42" s="3"/>
       <c r="AV42" s="3"/>
     </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="4" t="s">
         <v>99</v>
       </c>
       <c r="U43" s="3"/>
@@ -4252,11 +4298,11 @@
       <c r="AU43" s="3"/>
       <c r="AV43" s="3"/>
     </row>
-    <row r="44" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="1" t="s">
         <v>101</v>
       </c>
       <c r="U44" s="3"/>
@@ -4288,7 +4334,7 @@
       <c r="AU44" s="3"/>
       <c r="AV44" s="3"/>
     </row>
-    <row r="45" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>102</v>
       </c>
@@ -4324,7 +4370,7 @@
       <c r="AU45" s="3"/>
       <c r="AV45" s="3"/>
     </row>
-    <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>104</v>
       </c>
@@ -4360,7 +4406,7 @@
       <c r="AU46" s="3"/>
       <c r="AV46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>106</v>
       </c>
@@ -4396,7 +4442,7 @@
       <c r="AU47" s="3"/>
       <c r="AV47" s="3"/>
     </row>
-    <row r="48" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>108</v>
       </c>
@@ -4432,7 +4478,7 @@
       <c r="AU48" s="3"/>
       <c r="AV48" s="3"/>
     </row>
-    <row r="49" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>110</v>
       </c>
@@ -4468,15 +4514,12 @@
       <c r="AU49" s="3"/>
       <c r="AV49" s="3"/>
     </row>
-    <row r="50" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
         <v>112</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>113</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>114</v>
       </c>
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
@@ -4507,11 +4550,14 @@
       <c r="AU50" s="3"/>
       <c r="AV50" s="3"/>
     </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" s="4" t="s">
         <v>116</v>
       </c>
       <c r="U51" s="3"/>
@@ -4543,11 +4589,11 @@
       <c r="AU51" s="3"/>
       <c r="AV51" s="3"/>
     </row>
-    <row r="52" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="1" t="s">
         <v>118</v>
       </c>
       <c r="U52" s="3"/>
@@ -4615,31 +4661,13 @@
       <c r="AU53" s="3"/>
       <c r="AV53" s="3"/>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="s">
+    <row r="54" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="6"/>
-      <c r="M54" s="6"/>
-      <c r="N54" s="6"/>
-      <c r="O54" s="6"/>
-      <c r="P54" s="6"/>
-      <c r="Q54" s="6"/>
-      <c r="R54" s="6"/>
-      <c r="S54" s="6"/>
-      <c r="T54" s="6"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
@@ -4669,11 +4697,11 @@
       <c r="AU54" s="3"/>
       <c r="AV54" s="3"/>
     </row>
-    <row r="55" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="6" t="s">
         <v>124</v>
       </c>
       <c r="C55" s="6"/>
@@ -4723,7 +4751,7 @@
       <c r="AU55" s="3"/>
       <c r="AV55" s="3"/>
     </row>
-    <row r="56" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
         <v>125</v>
       </c>
@@ -4777,7 +4805,7 @@
       <c r="AU56" s="3"/>
       <c r="AV56" s="3"/>
     </row>
-    <row r="57" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
         <v>127</v>
       </c>
@@ -4831,7 +4859,7 @@
       <c r="AU57" s="3"/>
       <c r="AV57" s="3"/>
     </row>
-    <row r="58" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
         <v>129</v>
       </c>
@@ -4939,11 +4967,11 @@
       <c r="AU59" s="3"/>
       <c r="AV59" s="3"/>
     </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="4" t="s">
         <v>134</v>
       </c>
       <c r="C60" s="6"/>
@@ -4993,14 +5021,14 @@
       <c r="AU60" s="3"/>
       <c r="AV60" s="3"/>
     </row>
-    <row r="61" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C61" s="4"/>
+      <c r="C61" s="6"/>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
       <c r="F61" s="6"/>
@@ -5047,13 +5075,31 @@
       <c r="AU61" s="3"/>
       <c r="AV61" s="3"/>
     </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
+    <row r="62" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="4" t="s">
         <v>138</v>
       </c>
+      <c r="C62" s="4"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
+      <c r="M62" s="6"/>
+      <c r="N62" s="6"/>
+      <c r="O62" s="6"/>
+      <c r="P62" s="6"/>
+      <c r="Q62" s="6"/>
+      <c r="R62" s="6"/>
+      <c r="S62" s="6"/>
+      <c r="T62" s="6"/>
       <c r="U62" s="3"/>
       <c r="V62" s="3"/>
       <c r="W62" s="3"/>
@@ -5227,11 +5273,11 @@
       <c r="AU66" s="3"/>
       <c r="AV66" s="3"/>
     </row>
-    <row r="67" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="1" t="s">
         <v>148</v>
       </c>
       <c r="U67" s="3"/>
@@ -5263,11 +5309,11 @@
       <c r="AU67" s="3"/>
       <c r="AV67" s="3"/>
     </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="4" t="s">
         <v>150</v>
       </c>
       <c r="U68" s="3"/>
@@ -5299,11 +5345,11 @@
       <c r="AU68" s="3"/>
       <c r="AV68" s="3"/>
     </row>
-    <row r="69" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="1" t="s">
         <v>152</v>
       </c>
       <c r="U69" s="3"/>
@@ -5335,11 +5381,11 @@
       <c r="AU69" s="3"/>
       <c r="AV69" s="3"/>
     </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="4" t="s">
         <v>154</v>
       </c>
       <c r="U70" s="3"/>
@@ -5443,11 +5489,11 @@
       <c r="AU72" s="3"/>
       <c r="AV72" s="3"/>
     </row>
-    <row r="73" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="1" t="s">
         <v>160</v>
       </c>
       <c r="U73" s="3"/>
@@ -5479,9 +5525,12 @@
       <c r="AU73" s="3"/>
       <c r="AV73" s="3"/>
     </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
         <v>161</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>162</v>
       </c>
       <c r="U74" s="3"/>
       <c r="V74" s="3"/>
@@ -5512,11 +5561,8 @@
       <c r="AU74" s="3"/>
       <c r="AV74" s="3"/>
     </row>
-    <row r="75" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B75" s="4" t="s">
         <v>163</v>
       </c>
       <c r="U75" s="3"/>
@@ -5548,11 +5594,11 @@
       <c r="AU75" s="3"/>
       <c r="AV75" s="3"/>
     </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="4" t="s">
         <v>165</v>
       </c>
       <c r="U76" s="3"/>
@@ -5583,54 +5629,13 @@
       <c r="AT76" s="3"/>
       <c r="AU76" s="3"/>
       <c r="AV76" s="3"/>
-      <c r="AY76" s="3"/>
-      <c r="AZ76" s="3"/>
-      <c r="BA76" s="3"/>
-      <c r="BB76" s="3"/>
-      <c r="BC76" s="3"/>
-      <c r="BD76" s="3"/>
-      <c r="BE76" s="3"/>
-      <c r="BF76" s="3"/>
-      <c r="BG76" s="3"/>
-      <c r="BH76" s="3"/>
-      <c r="BI76" s="3"/>
-      <c r="BJ76" s="3"/>
-      <c r="BK76" s="3"/>
-      <c r="BL76" s="3"/>
-      <c r="BM76" s="3"/>
-      <c r="BN76" s="3"/>
-      <c r="BO76" s="3"/>
-      <c r="BP76" s="3"/>
-      <c r="BQ76" s="3"/>
-      <c r="BR76" s="3"/>
-      <c r="BS76" s="3"/>
-      <c r="BT76" s="3"/>
-      <c r="BU76" s="3"/>
-      <c r="BV76" s="3"/>
-      <c r="BW76" s="3"/>
-      <c r="BX76" s="3"/>
-      <c r="BY76" s="3"/>
-      <c r="BZ76" s="3"/>
-      <c r="CA76" s="3"/>
-      <c r="CB76" s="3"/>
-      <c r="CC76" s="3"/>
-      <c r="CD76" s="3"/>
-      <c r="CE76" s="3"/>
-      <c r="CF76" s="3"/>
-      <c r="CG76" s="3"/>
-      <c r="CH76" s="3"/>
-      <c r="CI76" s="3"/>
-      <c r="CJ76" s="3"/>
-      <c r="CK76" s="3"/>
-      <c r="CL76" s="3"/>
-      <c r="CM76" s="3"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
         <v>166</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="U77" s="3"/>
       <c r="V77" s="3"/>
@@ -5704,10 +5709,10 @@
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="U78" s="3"/>
       <c r="V78" s="3"/>
@@ -5779,11 +5784,11 @@
       <c r="CL78" s="3"/>
       <c r="CM78" s="3"/>
     </row>
-    <row r="79" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B79" s="1" t="s">
         <v>170</v>
       </c>
       <c r="U79" s="3"/>
@@ -5856,7 +5861,7 @@
       <c r="CL79" s="3"/>
       <c r="CM79" s="3"/>
     </row>
-    <row r="80" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
         <v>171</v>
       </c>
@@ -5933,7 +5938,7 @@
       <c r="CL80" s="3"/>
       <c r="CM80" s="3"/>
     </row>
-    <row r="81" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
         <v>173</v>
       </c>
@@ -6010,7 +6015,7 @@
       <c r="CL81" s="3"/>
       <c r="CM81" s="3"/>
     </row>
-    <row r="82" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
         <v>175</v>
       </c>
@@ -6087,7 +6092,7 @@
       <c r="CL82" s="3"/>
       <c r="CM82" s="3"/>
     </row>
-    <row r="83" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
         <v>177</v>
       </c>
@@ -6164,11 +6169,11 @@
       <c r="CL83" s="3"/>
       <c r="CM83" s="3"/>
     </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" s="4" t="s">
         <v>180</v>
       </c>
       <c r="U84" s="3"/>
@@ -6241,11 +6246,11 @@
       <c r="CL84" s="3"/>
       <c r="CM84" s="3"/>
     </row>
-    <row r="85" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="1" t="s">
         <v>182</v>
       </c>
       <c r="U85" s="3"/>
@@ -6318,11 +6323,11 @@
       <c r="CL85" s="3"/>
       <c r="CM85" s="3"/>
     </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" s="4" t="s">
         <v>184</v>
       </c>
       <c r="U86" s="3"/>
@@ -6780,11 +6785,11 @@
       <c r="CL91" s="3"/>
       <c r="CM91" s="3"/>
     </row>
-    <row r="92" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" s="1" t="s">
         <v>196</v>
       </c>
       <c r="U92" s="3"/>
@@ -6857,11 +6862,11 @@
       <c r="CL92" s="3"/>
       <c r="CM92" s="3"/>
     </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" s="4" t="s">
         <v>198</v>
       </c>
       <c r="U93" s="3"/>
@@ -6934,11 +6939,11 @@
       <c r="CL93" s="3"/>
       <c r="CM93" s="3"/>
     </row>
-    <row r="94" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="1" t="s">
         <v>200</v>
       </c>
       <c r="U94" s="3"/>
@@ -7011,13 +7016,41 @@
       <c r="CL94" s="3"/>
       <c r="CM94" s="3"/>
     </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B95" s="4" t="s">
         <v>202</v>
       </c>
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
+      <c r="AR95" s="3"/>
+      <c r="AS95" s="3"/>
+      <c r="AT95" s="3"/>
+      <c r="AU95" s="3"/>
+      <c r="AV95" s="3"/>
       <c r="AY95" s="3"/>
       <c r="AZ95" s="3"/>
       <c r="BA95" s="3"/>
@@ -7110,8 +7143,11 @@
       <c r="CM96" s="3"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="4" t="s">
+      <c r="A97" s="1" t="s">
         <v>205</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="AY97" s="3"/>
       <c r="AZ97" s="3"/>
@@ -7155,11 +7191,8 @@
       <c r="CL97" s="3"/>
       <c r="CM97" s="3"/>
     </row>
-    <row r="98" customFormat="false" ht="335.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B98" s="4" t="s">
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="4" t="s">
         <v>207</v>
       </c>
       <c r="AY98" s="3"/>
@@ -7204,11 +7237,11 @@
       <c r="CL98" s="3"/>
       <c r="CM98" s="3"/>
     </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="335.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B99" s="4" t="s">
         <v>209</v>
       </c>
       <c r="AY99" s="3"/>
@@ -7253,11 +7286,11 @@
       <c r="CL99" s="3"/>
       <c r="CM99" s="3"/>
     </row>
-    <row r="100" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" s="1" t="s">
         <v>211</v>
       </c>
       <c r="AY100" s="3"/>
@@ -7302,31 +7335,13 @@
       <c r="CL100" s="3"/>
       <c r="CM100" s="3"/>
     </row>
-    <row r="101" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="6" t="s">
+    <row r="101" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1" t="s">
         <v>212</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
-      <c r="J101" s="6"/>
-      <c r="K101" s="6"/>
-      <c r="L101" s="6"/>
-      <c r="M101" s="6"/>
-      <c r="N101" s="6"/>
-      <c r="O101" s="6"/>
-      <c r="P101" s="6"/>
-      <c r="Q101" s="6"/>
-      <c r="R101" s="6"/>
-      <c r="S101" s="6"/>
-      <c r="T101" s="6"/>
       <c r="AY101" s="3"/>
       <c r="AZ101" s="3"/>
       <c r="BA101" s="3"/>
@@ -7369,13 +7384,31 @@
       <c r="CL101" s="3"/>
       <c r="CM101" s="3"/>
     </row>
-    <row r="102" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1" t="s">
+    <row r="102" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="6" t="s">
         <v>214</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>215</v>
       </c>
+      <c r="C102" s="6"/>
+      <c r="D102" s="6"/>
+      <c r="E102" s="6"/>
+      <c r="F102" s="6"/>
+      <c r="G102" s="6"/>
+      <c r="H102" s="6"/>
+      <c r="I102" s="6"/>
+      <c r="J102" s="6"/>
+      <c r="K102" s="6"/>
+      <c r="L102" s="6"/>
+      <c r="M102" s="6"/>
+      <c r="N102" s="6"/>
+      <c r="O102" s="6"/>
+      <c r="P102" s="6"/>
+      <c r="Q102" s="6"/>
+      <c r="R102" s="6"/>
+      <c r="S102" s="6"/>
+      <c r="T102" s="6"/>
       <c r="AY102" s="3"/>
       <c r="AZ102" s="3"/>
       <c r="BA102" s="3"/>
@@ -7467,112 +7500,112 @@
       <c r="CL103" s="3"/>
       <c r="CM103" s="3"/>
     </row>
-    <row r="104" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
         <v>218</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="C104" s="1"/>
-      <c r="D104" s="1"/>
-      <c r="E104" s="1"/>
-      <c r="F104" s="1"/>
-      <c r="G104" s="1"/>
-      <c r="H104" s="1"/>
-      <c r="I104" s="1"/>
-      <c r="J104" s="1"/>
-      <c r="K104" s="1"/>
-      <c r="L104" s="1"/>
-      <c r="M104" s="1"/>
-      <c r="N104" s="1"/>
-      <c r="O104" s="1"/>
-      <c r="P104" s="1"/>
-      <c r="Q104" s="1"/>
-      <c r="R104" s="1"/>
-      <c r="S104" s="1"/>
-      <c r="T104" s="1"/>
-      <c r="U104" s="1"/>
-      <c r="V104" s="1"/>
-      <c r="W104" s="1"/>
-      <c r="X104" s="1"/>
-      <c r="Y104" s="1"/>
-      <c r="Z104" s="1"/>
-      <c r="AA104" s="1"/>
-      <c r="AB104" s="1"/>
-      <c r="AC104" s="1"/>
-      <c r="AD104" s="1"/>
-      <c r="AE104" s="1"/>
-      <c r="AF104" s="1"/>
-      <c r="AG104" s="1"/>
-      <c r="AH104" s="1"/>
-      <c r="AI104" s="1"/>
-      <c r="AJ104" s="1"/>
-      <c r="AK104" s="1"/>
-      <c r="AL104" s="1"/>
-      <c r="AM104" s="1"/>
-      <c r="AN104" s="1"/>
-      <c r="AO104" s="1"/>
-      <c r="AP104" s="1"/>
-      <c r="AQ104" s="1"/>
-      <c r="AR104" s="1"/>
-      <c r="AS104" s="1"/>
-      <c r="AT104" s="1"/>
-      <c r="AU104" s="1"/>
-      <c r="AV104" s="1"/>
-      <c r="AW104" s="1"/>
-      <c r="AX104" s="1"/>
-    </row>
-    <row r="105" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AY104" s="3"/>
+      <c r="AZ104" s="3"/>
+      <c r="BA104" s="3"/>
+      <c r="BB104" s="3"/>
+      <c r="BC104" s="3"/>
+      <c r="BD104" s="3"/>
+      <c r="BE104" s="3"/>
+      <c r="BF104" s="3"/>
+      <c r="BG104" s="3"/>
+      <c r="BH104" s="3"/>
+      <c r="BI104" s="3"/>
+      <c r="BJ104" s="3"/>
+      <c r="BK104" s="3"/>
+      <c r="BL104" s="3"/>
+      <c r="BM104" s="3"/>
+      <c r="BN104" s="3"/>
+      <c r="BO104" s="3"/>
+      <c r="BP104" s="3"/>
+      <c r="BQ104" s="3"/>
+      <c r="BR104" s="3"/>
+      <c r="BS104" s="3"/>
+      <c r="BT104" s="3"/>
+      <c r="BU104" s="3"/>
+      <c r="BV104" s="3"/>
+      <c r="BW104" s="3"/>
+      <c r="BX104" s="3"/>
+      <c r="BY104" s="3"/>
+      <c r="BZ104" s="3"/>
+      <c r="CA104" s="3"/>
+      <c r="CB104" s="3"/>
+      <c r="CC104" s="3"/>
+      <c r="CD104" s="3"/>
+      <c r="CE104" s="3"/>
+      <c r="CF104" s="3"/>
+      <c r="CG104" s="3"/>
+      <c r="CH104" s="3"/>
+      <c r="CI104" s="3"/>
+      <c r="CJ104" s="3"/>
+      <c r="CK104" s="3"/>
+      <c r="CL104" s="3"/>
+      <c r="CM104" s="3"/>
+    </row>
+    <row r="105" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
         <v>220</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="AY105" s="3"/>
-      <c r="AZ105" s="3"/>
-      <c r="BA105" s="3"/>
-      <c r="BB105" s="3"/>
-      <c r="BC105" s="3"/>
-      <c r="BD105" s="3"/>
-      <c r="BE105" s="3"/>
-      <c r="BF105" s="3"/>
-      <c r="BG105" s="3"/>
-      <c r="BH105" s="3"/>
-      <c r="BI105" s="3"/>
-      <c r="BJ105" s="3"/>
-      <c r="BK105" s="3"/>
-      <c r="BL105" s="3"/>
-      <c r="BM105" s="3"/>
-      <c r="BN105" s="3"/>
-      <c r="BO105" s="3"/>
-      <c r="BP105" s="3"/>
-      <c r="BQ105" s="3"/>
-      <c r="BR105" s="3"/>
-      <c r="BS105" s="3"/>
-      <c r="BT105" s="3"/>
-      <c r="BU105" s="3"/>
-      <c r="BV105" s="3"/>
-      <c r="BW105" s="3"/>
-      <c r="BX105" s="3"/>
-      <c r="BY105" s="3"/>
-      <c r="BZ105" s="3"/>
-      <c r="CA105" s="3"/>
-      <c r="CB105" s="3"/>
-      <c r="CC105" s="3"/>
-      <c r="CD105" s="3"/>
-      <c r="CE105" s="3"/>
-      <c r="CF105" s="3"/>
-      <c r="CG105" s="3"/>
-      <c r="CH105" s="3"/>
-      <c r="CI105" s="3"/>
-      <c r="CJ105" s="3"/>
-      <c r="CK105" s="3"/>
-      <c r="CL105" s="3"/>
-      <c r="CM105" s="3"/>
-    </row>
-    <row r="106" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1"/>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1"/>
+      <c r="K105" s="1"/>
+      <c r="L105" s="1"/>
+      <c r="M105" s="1"/>
+      <c r="N105" s="1"/>
+      <c r="O105" s="1"/>
+      <c r="P105" s="1"/>
+      <c r="Q105" s="1"/>
+      <c r="R105" s="1"/>
+      <c r="S105" s="1"/>
+      <c r="T105" s="1"/>
+      <c r="U105" s="1"/>
+      <c r="V105" s="1"/>
+      <c r="W105" s="1"/>
+      <c r="X105" s="1"/>
+      <c r="Y105" s="1"/>
+      <c r="Z105" s="1"/>
+      <c r="AA105" s="1"/>
+      <c r="AB105" s="1"/>
+      <c r="AC105" s="1"/>
+      <c r="AD105" s="1"/>
+      <c r="AE105" s="1"/>
+      <c r="AF105" s="1"/>
+      <c r="AG105" s="1"/>
+      <c r="AH105" s="1"/>
+      <c r="AI105" s="1"/>
+      <c r="AJ105" s="1"/>
+      <c r="AK105" s="1"/>
+      <c r="AL105" s="1"/>
+      <c r="AM105" s="1"/>
+      <c r="AN105" s="1"/>
+      <c r="AO105" s="1"/>
+      <c r="AP105" s="1"/>
+      <c r="AQ105" s="1"/>
+      <c r="AR105" s="1"/>
+      <c r="AS105" s="1"/>
+      <c r="AT105" s="1"/>
+      <c r="AU105" s="1"/>
+      <c r="AV105" s="1"/>
+      <c r="AW105" s="1"/>
+      <c r="AX105" s="1"/>
+    </row>
+    <row r="106" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
         <v>222</v>
       </c>
@@ -7621,42 +7654,65 @@
       <c r="CL106" s="3"/>
       <c r="CM106" s="3"/>
     </row>
-    <row r="107" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
         <v>224</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="108" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AY107" s="3"/>
+      <c r="AZ107" s="3"/>
+      <c r="BA107" s="3"/>
+      <c r="BB107" s="3"/>
+      <c r="BC107" s="3"/>
+      <c r="BD107" s="3"/>
+      <c r="BE107" s="3"/>
+      <c r="BF107" s="3"/>
+      <c r="BG107" s="3"/>
+      <c r="BH107" s="3"/>
+      <c r="BI107" s="3"/>
+      <c r="BJ107" s="3"/>
+      <c r="BK107" s="3"/>
+      <c r="BL107" s="3"/>
+      <c r="BM107" s="3"/>
+      <c r="BN107" s="3"/>
+      <c r="BO107" s="3"/>
+      <c r="BP107" s="3"/>
+      <c r="BQ107" s="3"/>
+      <c r="BR107" s="3"/>
+      <c r="BS107" s="3"/>
+      <c r="BT107" s="3"/>
+      <c r="BU107" s="3"/>
+      <c r="BV107" s="3"/>
+      <c r="BW107" s="3"/>
+      <c r="BX107" s="3"/>
+      <c r="BY107" s="3"/>
+      <c r="BZ107" s="3"/>
+      <c r="CA107" s="3"/>
+      <c r="CB107" s="3"/>
+      <c r="CC107" s="3"/>
+      <c r="CD107" s="3"/>
+      <c r="CE107" s="3"/>
+      <c r="CF107" s="3"/>
+      <c r="CG107" s="3"/>
+      <c r="CH107" s="3"/>
+      <c r="CI107" s="3"/>
+      <c r="CJ107" s="3"/>
+      <c r="CK107" s="3"/>
+      <c r="CL107" s="3"/>
+      <c r="CM107" s="3"/>
+    </row>
+    <row r="108" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
         <v>226</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C108" s="4"/>
-      <c r="D108" s="4"/>
-      <c r="E108" s="4"/>
-      <c r="F108" s="4"/>
-      <c r="G108" s="4"/>
-      <c r="H108" s="4"/>
-      <c r="I108" s="4"/>
-      <c r="J108" s="4"/>
-      <c r="K108" s="4"/>
-      <c r="L108" s="4"/>
-      <c r="M108" s="4"/>
-      <c r="N108" s="4"/>
-      <c r="O108" s="4"/>
-      <c r="P108" s="4"/>
-      <c r="Q108" s="4"/>
-      <c r="R108" s="4"/>
-      <c r="S108" s="4"/>
-      <c r="T108" s="4"/>
-    </row>
-    <row r="109" customFormat="false" ht="241.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="5" t="s">
+    </row>
+    <row r="109" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="1" t="s">
         <v>228</v>
       </c>
       <c r="B109" s="4" t="s">
@@ -7681,8 +7737,8 @@
       <c r="S109" s="4"/>
       <c r="T109" s="4"/>
     </row>
-    <row r="110" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="1" t="s">
+    <row r="110" customFormat="false" ht="241.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="5" t="s">
         <v>230</v>
       </c>
       <c r="B110" s="4" t="s">
@@ -7707,23 +7763,41 @@
       <c r="S110" s="4"/>
       <c r="T110" s="4"/>
     </row>
-    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="B111" s="4" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="112" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C111" s="4"/>
+      <c r="D111" s="4"/>
+      <c r="E111" s="4"/>
+      <c r="F111" s="4"/>
+      <c r="G111" s="4"/>
+      <c r="H111" s="4"/>
+      <c r="I111" s="4"/>
+      <c r="J111" s="4"/>
+      <c r="K111" s="4"/>
+      <c r="L111" s="4"/>
+      <c r="M111" s="4"/>
+      <c r="N111" s="4"/>
+      <c r="O111" s="4"/>
+      <c r="P111" s="4"/>
+      <c r="Q111" s="4"/>
+      <c r="R111" s="4"/>
+      <c r="S111" s="4"/>
+      <c r="T111" s="4"/>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="B112" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
         <v>236</v>
       </c>
@@ -7731,31 +7805,13 @@
         <v>237</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
         <v>238</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C114" s="4"/>
-      <c r="D114" s="4"/>
-      <c r="E114" s="4"/>
-      <c r="F114" s="4"/>
-      <c r="G114" s="4"/>
-      <c r="H114" s="4"/>
-      <c r="I114" s="4"/>
-      <c r="J114" s="4"/>
-      <c r="K114" s="4"/>
-      <c r="L114" s="4"/>
-      <c r="M114" s="4"/>
-      <c r="N114" s="4"/>
-      <c r="O114" s="4"/>
-      <c r="P114" s="4"/>
-      <c r="Q114" s="4"/>
-      <c r="R114" s="4"/>
-      <c r="S114" s="4"/>
-      <c r="T114" s="4"/>
     </row>
     <row r="115" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
@@ -7783,77 +7839,95 @@
       <c r="S115" s="4"/>
       <c r="T115" s="4"/>
     </row>
-    <row r="116" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
         <v>242</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C116" s="4"/>
+      <c r="D116" s="4"/>
+      <c r="E116" s="4"/>
+      <c r="F116" s="4"/>
+      <c r="G116" s="4"/>
+      <c r="H116" s="4"/>
+      <c r="I116" s="4"/>
+      <c r="J116" s="4"/>
+      <c r="K116" s="4"/>
+      <c r="L116" s="4"/>
+      <c r="M116" s="4"/>
+      <c r="N116" s="4"/>
+      <c r="O116" s="4"/>
+      <c r="P116" s="4"/>
+      <c r="Q116" s="4"/>
+      <c r="R116" s="4"/>
+      <c r="S116" s="4"/>
+      <c r="T116" s="4"/>
+    </row>
+    <row r="117" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D116" s="4" t="s">
+      <c r="B117" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="E116" s="4" t="s">
+      <c r="C117" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="F116" s="4" t="s">
+      <c r="D117" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="G116" s="4" t="s">
+      <c r="E117" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="H116" s="4" t="s">
+      <c r="F117" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="I116" s="4" t="s">
+      <c r="G117" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="J116" s="4" t="s">
+      <c r="H117" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="K116" s="4" t="s">
+      <c r="I117" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="L116" s="4" t="s">
+      <c r="J117" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="M116" s="4" t="s">
+      <c r="K117" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="N116" s="4" t="s">
+      <c r="L117" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="O116" s="4" t="s">
+      <c r="M117" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="P116" s="4" t="s">
+      <c r="N117" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="Q116" s="4" t="s">
+      <c r="O117" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="R116" s="4" t="s">
+      <c r="P117" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="S116" s="4" t="s">
+      <c r="Q117" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="T116" s="4" t="s">
+      <c r="R117" s="4" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="117" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="1" t="s">
+      <c r="S117" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="T117" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
         <v>264</v>
       </c>
@@ -7861,41 +7935,41 @@
         <v>265</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="6" t="s">
+    <row r="119" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="1" t="s">
         <v>266</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="C119" s="6"/>
-      <c r="D119" s="6"/>
-      <c r="E119" s="6"/>
-      <c r="F119" s="6"/>
-      <c r="G119" s="6"/>
-      <c r="H119" s="6"/>
-      <c r="I119" s="6"/>
-      <c r="J119" s="6"/>
-      <c r="K119" s="6"/>
-      <c r="L119" s="6"/>
-      <c r="M119" s="6"/>
-      <c r="N119" s="6"/>
-      <c r="O119" s="6"/>
-      <c r="P119" s="6"/>
-      <c r="Q119" s="6"/>
-      <c r="R119" s="6"/>
-      <c r="S119" s="6"/>
-      <c r="T119" s="6"/>
-    </row>
-    <row r="120" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="1" t="s">
+    </row>
+    <row r="120" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="B120" s="8" t="s">
+      <c r="B120" s="4" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="121" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C120" s="6"/>
+      <c r="D120" s="6"/>
+      <c r="E120" s="6"/>
+      <c r="F120" s="6"/>
+      <c r="G120" s="6"/>
+      <c r="H120" s="6"/>
+      <c r="I120" s="6"/>
+      <c r="J120" s="6"/>
+      <c r="K120" s="6"/>
+      <c r="L120" s="6"/>
+      <c r="M120" s="6"/>
+      <c r="N120" s="6"/>
+      <c r="O120" s="6"/>
+      <c r="P120" s="6"/>
+      <c r="Q120" s="6"/>
+      <c r="R120" s="6"/>
+      <c r="S120" s="6"/>
+      <c r="T120" s="6"/>
+    </row>
+    <row r="121" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
         <v>270</v>
       </c>
@@ -7903,85 +7977,85 @@
         <v>271</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="B122" s="8" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B123" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="C123" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="H123" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="I123" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="J123" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="K123" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="L123" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="M123" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="N123" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="O123" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="P123" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q123" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="R123" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="S123" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="T123" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B124" s="4" t="s">
+      <c r="B124" s="1" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="125" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="K124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="L124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="M124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="N124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="O124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="P124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="R124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="S124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="T124" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
         <v>278</v>
       </c>
@@ -7989,11 +8063,11 @@
         <v>279</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B126" s="4" t="s">
         <v>281</v>
       </c>
     </row>
@@ -8005,15 +8079,15 @@
         <v>283</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B128" s="4" t="s">
+      <c r="B128" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
         <v>286</v>
       </c>
@@ -8021,7 +8095,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
         <v>288</v>
       </c>
@@ -8037,7 +8111,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
         <v>292</v>
       </c>
@@ -8045,31 +8119,31 @@
         <v>293</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
         <v>294</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B135" s="8" t="s">
+      <c r="B135" s="4" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
         <v>299</v>
       </c>
@@ -8077,16 +8151,24 @@
         <v>300</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B137" s="4" t="s">
+      <c r="B137" s="8" t="s">
         <v>302</v>
       </c>
     </row>
+    <row r="138" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>304</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:T136"/>
+  <autoFilter ref="A2:T137"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
